--- a/backend/dependency_table_repo.xlsx
+++ b/backend/dependency_table_repo.xlsx
@@ -443,27 +443,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Controller.php</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>CreateCapsuleController.php, DashboardController.php, ProfileController.php, PublicWallController.php, ViewCapsuleController.php, AuthController.php</t>
-        </is>
-      </c>
+          <t>AuthController.php</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CreateCapsuleController.php</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
+          <t>Controller.php</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CapsuleController.php, EmailController.php, MediaController.php, UserController.php</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DashboardController.php</t>
+          <t>CapsuleController.php</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -471,7 +471,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ProfileController.php</t>
+          <t>EmailController.php</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -479,7 +479,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PublicWallController.php</t>
+          <t>MediaController.php</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -487,7 +487,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ViewCapsuleController.php</t>
+          <t>UserController.php</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -495,80 +495,84 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AuthController.php</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
+          <t>Capsule.php</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CapsuleController.php, CapsuleService.php, MediaService.php</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capsule.php</t>
+          <t>Email.php</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DashboardController.php, PublicWallController.php, ViewCapsuleController.php, CapsuleRevealService.php, CapsuleService.php</t>
+          <t>EmailController.php</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>User.php</t>
+          <t>Media.php</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ProfileController.php, PublicWallController.php, UserService.php, AuthService.php</t>
+          <t>MediaController.php, MediaService.php</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CapsuleRevealService.php</t>
+          <t>User.php</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DashboardController.php, PublicWallController.php</t>
+          <t>AuthService.php, UserController.php</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CapsuleService.php</t>
+          <t>AuthService.php</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CreateCapsuleController.php</t>
+          <t>AuthController.php</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UserService.php</t>
+          <t>CapsuleService.php</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ProfileController.php</t>
+          <t>CapsuleController.php</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AuthService.php</t>
+          <t>MediaService.php</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AuthController.php</t>
+          <t>MediaController.php</t>
         </is>
       </c>
     </row>

--- a/backend/dependency_table_repo.xlsx
+++ b/backend/dependency_table_repo.xlsx
@@ -425,154 +425,220 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>File</t>
+          <t>File ID</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Used By</t>
+          <t>File Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Used By (File IDs)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>AuthController.php</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>Controller.php</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>CapsuleController.php, EmailController.php, MediaController.php, UserController.php</t>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>6, 7, 8, 9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>CapsuleController.php</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>EmailController.php</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>MediaController.php</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>UserController.php</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>Capsule.php</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CapsuleController.php, CapsuleService.php, MediaService.php</t>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6, 17, 18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Email.php</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>EmailController.php</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Media.php</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>MediaController.php, MediaService.php</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>8, 18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>User.php</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>AuthService.php, UserController.php</t>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>AuthService.php</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>AuthController.php</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>CapsuleService.php</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CapsuleController.php</t>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>MediaService.php</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>MediaController.php</t>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
     </row>

--- a/backend/dependency_table_repo.xlsx
+++ b/backend/dependency_table_repo.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>651</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -461,7 +461,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>652</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,14 +471,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6, 7, 8, 9</t>
+          <t>653, 654, 655, 656</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -491,7 +491,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>654</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -504,7 +504,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>655</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -517,7 +517,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>656</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>658</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -540,14 +540,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6, 17, 18</t>
+          <t>653, 664, 665</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>659</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -560,7 +560,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>660</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -570,14 +570,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8, 18</t>
+          <t>655, 665</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>661</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -587,14 +587,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>663</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>663</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -604,14 +604,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>651</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>664</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -621,14 +621,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>653</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>665</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>655</t>
         </is>
       </c>
     </row>

--- a/backend/dependency_table_repo.xlsx
+++ b/backend/dependency_table_repo.xlsx
@@ -448,42 +448,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>347</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AuthController.php</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>Controller.php</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>348, 349, 350, 351, 352, 353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>348</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Controller.php</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>653, 654, 655, 656</t>
-        </is>
-      </c>
+          <t>CreateCapsuleController.php</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>349</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CapsuleController.php</t>
+          <t>DashboardController.php</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -491,12 +491,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>350</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EmailController.php</t>
+          <t>ProfileController.php</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -504,12 +504,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>351</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MediaController.php</t>
+          <t>PublicWallController.php</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -517,12 +517,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>352</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UserController.php</t>
+          <t>ViewCapsuleController.php</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -530,115 +530,115 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>353</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capsule.php</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>653, 664, 665</t>
-        </is>
-      </c>
+          <t>AuthController.php</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>355</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Email.php</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Capsule.php</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>349, 351, 352, 358, 359</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>356</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Media.php</t>
+          <t>User.php</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>655, 665</t>
+          <t>350, 351, 360, 361</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>661</t>
+          <t>358</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>User.php</t>
+          <t>CapsuleRevealService.php</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>349, 351</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>359</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AuthService.php</t>
+          <t>CapsuleService.php</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>651</t>
+          <t>348</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>360</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CapsuleService.php</t>
+          <t>UserService.php</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>350</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>361</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MediaService.php</t>
+          <t>AuthService.php</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>353</t>
         </is>
       </c>
     </row>

--- a/backend/dependency_table_repo.xlsx
+++ b/backend/dependency_table_repo.xlsx
@@ -448,42 +448,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>347</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Controller.php</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>348, 349, 350, 351, 352, 353</t>
-        </is>
-      </c>
+          <t>AuthController.php</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CreateCapsuleController.php</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Controller.php</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1025, 1026, 1027, 1028</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>349</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DashboardController.php</t>
+          <t>CapsuleController.php</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -491,12 +491,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ProfileController.php</t>
+          <t>EmailController.php</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -504,12 +504,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>351</t>
+          <t>1027</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>PublicWallController.php</t>
+          <t>MediaController.php</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -517,12 +517,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>1028</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ViewCapsuleController.php</t>
+          <t>UserController.php</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -530,115 +530,115 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AuthController.php</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Capsule.php</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1025, 1036, 1037</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capsule.php</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>349, 351, 352, 358, 359</t>
-        </is>
-      </c>
+          <t>Email.php</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>User.php</t>
+          <t>Media.php</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>350, 351, 360, 361</t>
+          <t>1027, 1037</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CapsuleRevealService.php</t>
+          <t>User.php</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>349, 351</t>
+          <t>1035</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CapsuleService.php</t>
+          <t>AuthService.php</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>1023</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UserService.php</t>
+          <t>CapsuleService.php</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1025</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AuthService.php</t>
+          <t>MediaService.php</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>353</t>
+          <t>1027</t>
         </is>
       </c>
     </row>

--- a/backend/dependency_table_repo.xlsx
+++ b/backend/dependency_table_repo.xlsx
@@ -448,42 +448,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AuthController.php</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>connection.php</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1084, 1085, 1086, 1087, 1088, 1089, 1090, 1091</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Controller.php</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1025, 1026, 1027, 1028</t>
-        </is>
-      </c>
+          <t>AuditoriumController.php</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CapsuleController.php</t>
+          <t>AuthController.php</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -491,12 +491,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1086</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EmailController.php</t>
+          <t>BookedSeatController.php</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -504,12 +504,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MediaController.php</t>
+          <t>BookingController.php</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -517,12 +517,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UserController.php</t>
+          <t>MovieController.php</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
@@ -530,29 +530,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1030</t>
+          <t>1089</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capsule.php</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1025, 1036, 1037</t>
-        </is>
-      </c>
+          <t>SeatController.php</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Email.php</t>
+          <t>ShowtimeController.php</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
@@ -560,85 +556,81 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1091</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Media.php</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>1027, 1037</t>
-        </is>
-      </c>
+          <t>UserController.php</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>User.php</t>
+          <t>Auditorium.php</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1084, 1089, 1090</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AuthService.php</t>
+          <t>Booking.php</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1087, 1090</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CapsuleService.php</t>
+          <t>BookingSeat.php</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>1086, 1087</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MediaService.php</t>
+          <t>BookingSnack.php</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1087</t>
         </is>
       </c>
     </row>

--- a/backend/dependency_table_repo.xlsx
+++ b/backend/dependency_table_repo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,42 +448,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>connection.php</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1084, 1085, 1086, 1087, 1088, 1089, 1090, 1091</t>
-        </is>
-      </c>
+          <t>AuthController.php</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AuditoriumController.php</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Controller.php</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1247, 1248, 1249, 1250</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1247</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AuthController.php</t>
+          <t>CapsuleController.php</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
@@ -491,12 +491,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1248</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BookedSeatController.php</t>
+          <t>EmailController.php</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -504,12 +504,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BookingController.php</t>
+          <t>MediaController.php</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
@@ -517,122 +517,15 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MovieController.php</t>
+          <t>UserController.php</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>1089</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SeatController.php</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>1090</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ShowtimeController.php</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>1091</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>UserController.php</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Auditorium.php</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1084, 1089, 1090</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Booking.php</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1087, 1090</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BookingSeat.php</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1086, 1087</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BookingSnack.php</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1087</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
